--- a/crates/xlstream-eval/tests/fixtures/date/workdays.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/date/workdays.xlsx
@@ -21,12 +21,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t xml:space="preserve">networkdays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">workday</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t xml:space="preserve">start_serial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">end_serial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">netdays_no_hol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">netdays_with_hol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">workday_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">workday_neg5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">workday_with_hol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">holiday</t>
   </si>
 </sst>
 </file>
@@ -299,7 +317,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -309,15 +327,160 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <f aca="false">NETWORKDAYS(DATE(2026,1,1),DATE(2026,1,31))</f>
+        <v>46023</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A2,B2)</f>
         <v>22</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <f aca="false">WORKDAY(DATE(2026,1,1),10)</f>
+      <c r="D2" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A2,B2,Holidays!A2:A4)</f>
+        <v>19</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <f aca="false">WORKDAY(A2,10)</f>
         <v>46037</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <f aca="false">WORKDAY(A2,-5)</f>
+        <v>46016</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <f aca="false">WORKDAY(A2,10,Holidays!A2:A4)</f>
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A3,B3)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A3,B3,Holidays!A2:A4)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <f aca="false">WORKDAY(A3,10)</f>
+        <v>46037</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <f aca="false">WORKDAY(A3,-5)</f>
+        <v>46016</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <f aca="false">WORKDAY(A3,10,Holidays!A2:A4)</f>
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>46024</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A4,B4)</f>
+        <v>2</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A4,B4,Holidays!A2:A4)</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <f aca="false">WORKDAY(A4,10)</f>
+        <v>46037</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">WORKDAY(A4,-5)</f>
+        <v>46016</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <f aca="false">WORKDAY(A4,10,Holidays!A2:A4)</f>
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>46026</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A5,B5)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A5,B5,Holidays!A2:A4)</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false">WORKDAY(A5,10)</f>
+        <v>46037</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false">WORKDAY(A5,-5)</f>
+        <v>46016</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <f aca="false">WORKDAY(A5,10,Holidays!A2:A4)</f>
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>46053</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A6,B6)</f>
+        <v>22</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <f aca="false">NETWORKDAYS(A6,B6,Holidays!A2:A4)</f>
+        <v>19</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <f aca="false">WORKDAY(A6,10)</f>
+        <v>46037</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">WORKDAY(A6,-5)</f>
+        <v>46016</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <f aca="false">WORKDAY(A6,10,Holidays!A2:A4)</f>
+        <v>46041</v>
       </c>
     </row>
   </sheetData>
@@ -336,22 +499,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
-        <v>46023</v>
+      <c r="A1" s="0" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>46054</v>
+        <v>46024</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>46388</v>
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>46051</v>
       </c>
     </row>
   </sheetData>
